--- a/data/ams_weekly_data/White_Mulberry/ads_report_week16.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week16.xlsx
@@ -3871,7 +3871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3930,23 +3930,23 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>922</v>
+        <v>1844</v>
       </c>
       <c r="E2" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="F2" t="n">
-        <v>91.30500000000001</v>
+        <v>182.61</v>
       </c>
       <c r="G2" t="n">
-        <v>3558.9</v>
+        <v>7117.8</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3958,28 +3958,28 @@
       <c r="A3" t="inlineStr"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- Product collection- exact /Reach</t>
+          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>922</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>91.30500000000001</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>3558.9</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3996,11 +3996,11 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>8.666666666666666</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -4029,11 +4029,11 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>8.666666666666666</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Camb-SB-Multiple Asin- product collection- Reach</t>
+          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8.666666666666666</v>
+        <v>9285</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4166666666666667</v>
+        <v>560.2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4090,63 +4090,30 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>WM- SBV- Wooden Arm- B0DP32F346- Phrase</t>
+          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DB5VG39T</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9285</v>
+        <v>30315</v>
       </c>
       <c r="E7" t="n">
-        <v>56</v>
+        <v>257</v>
       </c>
       <c r="F7" t="n">
-        <v>560.2</v>
+        <v>2750.01</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3982.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>WM-SBV-Gas Spring MA- B0DB5VG39T- Phrase</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>B0DB5VG39T</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>30315</v>
-      </c>
-      <c r="E8" t="n">
-        <v>257</v>
-      </c>
-      <c r="F8" t="n">
-        <v>2750.01</v>
-      </c>
-      <c r="G8" t="n">
-        <v>3982.2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="inlineStr">
         <is>
           <t>White Mulberry</t>
         </is>

--- a/data/ams_weekly_data/White_Mulberry/ads_report_week16.xlsx
+++ b/data/ams_weekly_data/White_Mulberry/ads_report_week16.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
